--- a/Dataset/IT/xlsx/ITAMed_2018.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2018.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione</t>
+          <t>Anestesia e Rianimazione; Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Gastroenterologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Gastroenterologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Malattie Infettive</t>
+          <t>Malattie Infettive; Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Endocrinologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Medicina Legale</t>
+          <t>Igiene, Epidemiologia e Statistica; Medicina Legale</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Nefrologia</t>
+          <t>Nefrologia; Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Farmacologia e Tossicologia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Endocrinologia; Nefrologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Nefrologia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Pneumologia e Chirurgia Toracica</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Nefrologia; Endocrinologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Ginecologia e Ostetricia</t>
+          <t>Dermatologia e Venereologia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Nefrologia; Farmacologia e Tossicologia</t>
+          <t>Nefrologia</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Nefrologia; Immunologia e Reumatologia</t>
+          <t>Immunologia e Reumatologia; Nefrologia</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Oncologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Oftalmologia; Pediatria</t>
+          <t>Oftalmologia</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Oncologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Pediatria</t>
+          <t>Otorinolaringoiatria; Pediatria</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Oncologia</t>
+          <t>Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2018.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2018.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/IT/xlsx/ITAMed_2018.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2018.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.7890625" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -478,15 +478,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Tipo Domanda</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -549,6 +554,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -607,6 +617,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -665,6 +680,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -723,6 +743,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -781,6 +806,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -839,6 +869,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -897,6 +932,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -955,6 +995,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1013,6 +1058,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1071,6 +1121,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1129,6 +1184,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1187,6 +1247,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1245,6 +1310,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1303,6 +1373,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1361,6 +1436,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1419,6 +1499,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1477,6 +1562,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1535,6 +1625,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1593,6 +1688,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1651,6 +1751,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1709,6 +1814,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1767,6 +1877,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1825,6 +1940,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1883,6 +2003,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1941,6 +2066,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1999,6 +2129,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2057,6 +2192,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2115,6 +2255,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2175,10 +2320,15 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>images/2018/ssm20182143254.png</t>
         </is>
@@ -2241,6 +2391,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2299,6 +2454,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2357,6 +2517,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2415,6 +2580,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2473,6 +2643,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2531,6 +2706,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2589,6 +2769,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2647,6 +2832,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2705,6 +2895,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2763,6 +2958,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2821,6 +3021,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2879,6 +3084,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2937,6 +3147,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2995,6 +3210,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3053,6 +3273,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3111,6 +3336,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3169,6 +3399,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3227,6 +3462,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3285,6 +3525,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3343,6 +3588,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3401,6 +3651,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3459,6 +3714,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3517,6 +3777,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3575,6 +3840,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3633,6 +3903,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3691,6 +3966,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3749,6 +4029,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3807,6 +4092,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3867,10 +4157,15 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
           <t>Histological image</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>images/2018/ssm20182144704.png</t>
         </is>
@@ -3933,6 +4228,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3993,10 +4293,15 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>images/2018/ssm20182144804.png</t>
         </is>
@@ -4059,6 +4364,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4117,6 +4427,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4175,6 +4490,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4233,6 +4553,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4291,6 +4616,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4349,6 +4679,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4407,6 +4742,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4465,6 +4805,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4523,6 +4868,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4581,6 +4931,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4639,6 +4994,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4697,6 +5057,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4757,10 +5122,15 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>images/2018/ssm20182145454.png</t>
         </is>
@@ -4825,10 +5195,15 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>images/2018/ssm20182145504.png</t>
         </is>
@@ -4891,6 +5266,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4949,6 +5329,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5007,6 +5392,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5065,6 +5455,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5123,6 +5518,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5181,6 +5581,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5239,6 +5644,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5297,6 +5707,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5355,6 +5770,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5413,6 +5833,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5471,6 +5896,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5529,6 +5959,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5587,6 +6022,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5645,6 +6085,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5705,10 +6150,15 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
           <t>Forensic photograph</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>images/2018/ssm20182146254.png</t>
         </is>
@@ -5771,6 +6221,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5829,6 +6284,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5887,6 +6347,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5945,6 +6410,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6003,6 +6473,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6063,10 +6538,15 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>images/2018/ssm20182146554.png</t>
         </is>
@@ -6131,10 +6611,15 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
           <t>Brain MRI</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>images/2018/ssm20182146604.png</t>
         </is>
@@ -6197,6 +6682,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6255,6 +6745,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6313,6 +6808,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6371,6 +6871,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6429,6 +6934,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6487,6 +6997,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6545,6 +7060,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6603,6 +7123,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6661,6 +7186,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6719,6 +7249,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6777,6 +7312,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6835,6 +7375,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6893,6 +7438,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6953,10 +7503,15 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
           <t>Lower limb X-ray</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>images/2018/ssm20182147304.png</t>
         </is>
@@ -7019,6 +7574,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7077,6 +7637,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7135,6 +7700,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7193,6 +7763,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7251,6 +7826,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7309,6 +7889,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7367,6 +7952,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7425,6 +8015,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7483,6 +8078,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7541,6 +8141,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7599,6 +8204,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7657,6 +8267,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7715,6 +8330,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7773,6 +8393,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7831,6 +8456,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7889,6 +8519,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7947,6 +8582,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8005,6 +8645,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8063,6 +8708,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8121,6 +8771,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8179,6 +8834,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8237,6 +8897,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8295,6 +8960,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8353,6 +9023,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8411,6 +9086,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8469,6 +9149,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8527,6 +9212,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8585,6 +9275,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8643,6 +9338,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8699,6 +9399,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>case-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
